--- a/lab3/out/lab3_recalculated.xlsx
+++ b/lab3/out/lab3_recalculated.xlsx
@@ -2980,8 +2980,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3100,7 +3101,7 @@
         <v>6.19047619047619</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>210</v>
       </c>
@@ -3693,20 +3694,20 @@
   <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>185</v>
       </c>
@@ -4037,7 +4038,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>246</v>
       </c>
@@ -4081,7 +4082,7 @@
         <v>30468.0124223603</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>248</v>
       </c>
@@ -4572,7 +4573,7 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="3" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="11"/>
   </cols>
@@ -5118,7 +5119,7 @@
         <v>9600</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>304</v>
       </c>
@@ -5147,11 +5148,10 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5551,7 +5551,7 @@
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
     </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>325</v>
       </c>

--- a/lab3/out/lab3_recalculated.xlsx
+++ b/lab3/out/lab3_recalculated.xlsx
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="333">
   <si>
     <t xml:space="preserve">Ім'я</t>
   </si>
@@ -612,43 +612,46 @@
     <t xml:space="preserve">Support і change після релізу</t>
   </si>
   <si>
-    <t xml:space="preserve">support 0,25 DevOps + 0,25 BA/PM; change 0,5 Developer + 0,25 QA</t>
+    <t xml:space="preserve">support 0,25 DevOps + 0,25 BA/PM (чергування, оновлення, онбординг нових будівель); change 0,5 Developer + 0,25 QA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">однаково для обох сценаріїв; підтримка будівлі (консультації клієнта, перевірка нестабільних лічильників) є змінною витратою 4,80 EUR у COGS ЛР № 1 і в support не дублюється</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пострелізні ризики</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cloud 30% × 20% річного cloud; альтернатива 10% × (5 000 + 10 днів DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">різні механізми ризику сценаріїв</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 днів DevOps; для альтернативи ще 700 EUR на демонтаж і знищення дисків</t>
+  </si>
+  <si>
+    <t xml:space="preserve">в кінці Y3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Інфляція і горизонт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">постійні ціни EUR, без індексації; 3 роки експлуатації після релізу</t>
   </si>
   <si>
     <t xml:space="preserve">однаково для обох сценаріїв</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пострелізні ризики</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cloud 30% × 20% річного cloud; альтернатива 10% × (5 000 + 10 днів DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">різні механізми ризику сценаріїв</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retirement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 днів DevOps; для альтернативи ще 700 EUR на демонтаж і знищення дисків</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в кінці Y3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Інфляція і горизонт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">постійні ціни EUR, без індексації; 3 роки експлуатації після релізу</t>
   </si>
   <si>
     <t xml:space="preserve">Роль</t>
@@ -2630,7 +2633,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>170</v>
       </c>
@@ -2695,7 +2698,7 @@
         <v>52</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2727,36 +2730,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B2" s="7" t="n">
         <f aca="false">x_rate_BA</f>
@@ -2793,7 +2796,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B3" s="7" t="n">
         <f aca="false">x_rate_UX</f>
@@ -2830,7 +2833,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B4" s="7" t="n">
         <f aca="false">x_rate_DEV</f>
@@ -2867,7 +2870,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B5" s="7" t="n">
         <f aca="false">x_rate_QA</f>
@@ -2904,7 +2907,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">x_rate_OPS</f>
@@ -2949,7 +2952,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B9" s="7" t="n">
         <f aca="false">x_min_wage*x_cap_mult/x_fx</f>
@@ -2987,24 +2990,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B2" s="10" t="n">
         <f aca="false">0</f>
@@ -3025,7 +3028,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B3" s="10" t="n">
         <f aca="false">x_ef11</f>
@@ -3046,7 +3049,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B4" s="10" t="n">
         <f aca="false">x_ef12</f>
@@ -3067,7 +3070,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B5" s="10" t="n">
         <f aca="false">x_fc</f>
@@ -3088,7 +3091,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -3103,42 +3106,42 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">EDATE(DATE(2026,11,1),0)</f>
@@ -3182,7 +3185,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">EDATE(DATE(2026,11,1),1)</f>
@@ -3227,7 +3230,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">EDATE(DATE(2026,11,1),2)</f>
@@ -3272,7 +3275,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">EDATE(DATE(2026,11,1),3)</f>
@@ -3317,7 +3320,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B13" s="11" t="n">
         <f aca="false">EDATE(DATE(2026,11,1),4)</f>
@@ -3362,7 +3365,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">EDATE(DATE(2026,11,1),5)</f>
@@ -3407,7 +3410,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B15" s="11" t="n">
         <f aca="false">EDATE(DATE(2026,11,1),6)</f>
@@ -3452,7 +3455,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">EDATE(DATE(2026,11,1),7)</f>
@@ -3497,7 +3500,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B17" s="11" t="n">
         <f aca="false">EDATE(DATE(2026,11,1),8)</f>
@@ -3542,7 +3545,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B18" s="11" t="n">
         <f aca="false">EDATE(DATE(2026,11,1),9)</f>
@@ -3587,7 +3590,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">EDATE(DATE(2026,11,1),10)</f>
@@ -3632,7 +3635,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">EDATE(DATE(2026,11,1),11)</f>
@@ -3709,48 +3712,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B2" s="12" t="n">
         <f aca="false">x_rate_BA</f>
@@ -3798,7 +3801,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B3" s="12" t="n">
         <f aca="false">x_rate_UX</f>
@@ -3846,7 +3849,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B4" s="12" t="n">
         <f aca="false">x_rate_DEV</f>
@@ -3894,7 +3897,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B5" s="12" t="n">
         <f aca="false">x_rate_QA</f>
@@ -3942,7 +3945,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B6" s="12" t="n">
         <f aca="false">x_rate_OPS</f>
@@ -3990,7 +3993,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="9" t="n">
@@ -4040,7 +4043,7 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="15" t="n">
@@ -4062,7 +4065,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="15" t="n">
@@ -4084,7 +4087,7 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="15" t="n">
@@ -4124,24 +4127,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>1</v>
@@ -4152,10 +4155,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>2</v>
@@ -4166,10 +4169,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>4</v>
@@ -4180,10 +4183,10 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>1</v>
@@ -4194,10 +4197,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>2</v>
@@ -4208,10 +4211,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>4</v>
@@ -4222,10 +4225,10 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>6</v>
@@ -4236,10 +4239,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>1</v>
@@ -4250,10 +4253,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>2</v>
@@ -4264,10 +4267,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>3</v>
@@ -4278,10 +4281,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>4</v>
@@ -4292,10 +4295,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>5</v>
@@ -4306,10 +4309,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>6</v>
@@ -4320,10 +4323,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>7</v>
@@ -4337,30 +4340,30 @@
         <v>125</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C18" s="16" t="n">
         <f aca="false">x_r1_p</f>
@@ -4385,10 +4388,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C19" s="16" t="n">
         <f aca="false">x_r2_p</f>
@@ -4403,7 +4406,7 @@
         <v>3712.35632183908</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G19" s="8" t="n">
         <f aca="false">1-(1-x_r2_turnover)^(2*x_months_total/12)</f>
@@ -4412,43 +4415,43 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B22" s="7" t="n">
         <f aca="false">x_labor</f>
         <v>120358.333333333</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B23" s="7" t="n">
         <f aca="false">SUMIF(A2:A15,"Обладнання",D2:D15)</f>
         <v>4000</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>66</v>
@@ -4456,14 +4459,14 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B24" s="7" t="n">
         <f aca="false">SUMIF(A2:A15,"Ліцензії",D2:D15)</f>
         <v>7000</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>66</v>
@@ -4471,14 +4474,14 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B25" s="7" t="n">
         <f aca="false">SUMIF(A2:A15,"Cloud розроблення",D2:D15)</f>
         <v>4000</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>66</v>
@@ -4486,7 +4489,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B26" s="7" t="n">
         <f aca="false">SUM(B22:B25)</f>
@@ -4494,27 +4497,27 @@
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B27" s="7" t="n">
         <f aca="false">SUM(E18:E19)</f>
         <v>10112.3563218391</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B28" s="7" t="n">
         <f aca="false">B26+B27</f>
@@ -4522,27 +4525,27 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B29" s="7" t="n">
         <f aca="false">D18-E18</f>
         <v>9600</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B30" s="7" t="n">
         <f aca="false">B28+B29</f>
@@ -4550,7 +4553,7 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -4580,51 +4583,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B2" s="15" t="n">
         <f aca="false">SUMPRODUCT('Календар і фази'!G9:J9,Labor!$C$9:$F$9)</f>
@@ -4681,7 +4684,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B3" s="15" t="n">
         <f aca="false">SUMIF('Baseline MVP'!$C$2:$C$15,1,'Baseline MVP'!$D$2:$D$15)-SUMIFS('Baseline MVP'!$D$2:$D$15,'Baseline MVP'!$C$2:$C$15,1,'Baseline MVP'!$A$2:$A$15,"Cloud розроблення")</f>
@@ -4738,7 +4741,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B4" s="15" t="n">
         <f aca="false">SUMIFS('Baseline MVP'!$D$2:$D$15,'Baseline MVP'!$C$2:$C$15,1,'Baseline MVP'!$A$2:$A$15,"Cloud розроблення")+x_cloud_y1/12*'Календар і фази'!K9</f>
@@ -4852,7 +4855,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B6" s="15" t="n">
         <f aca="false">SUMIF('Baseline MVP'!$F$18:$F$19,1,'Baseline MVP'!$E$18:$E$19)</f>
@@ -4909,7 +4912,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B7" s="15" t="n">
         <f aca="false">SUM(B2:B6)</f>
@@ -4966,7 +4969,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B8" s="15" t="n">
         <f aca="false">B7</f>
@@ -5020,7 +5023,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">B7-x_cloud_y1/12*'Календар і фази'!K9+x_alt_op/12*'Календар і фази'!K9+IF(1=x_alt_month,x_alt_start,0)</f>
@@ -5085,7 +5088,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B12" s="7" t="n">
         <f aca="false">x_cont</f>
@@ -5094,7 +5097,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B13" s="7" t="n">
         <f aca="false">N6</f>
@@ -5103,7 +5106,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B14" s="7" t="n">
         <f aca="false">B12-B13</f>
@@ -5112,7 +5115,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B15" s="7" t="n">
         <f aca="false">x_mr</f>
@@ -5121,7 +5124,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B16" s="9" t="str">
         <f aca="false">"M7, "&amp;TEXT(WORKDAY(x_start,x_bl_days-1,x_holidays),"DD.MM.YYYY")</f>
@@ -5156,39 +5159,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B2" s="15" t="n">
         <f aca="false">x_cbl</f>
@@ -5222,7 +5225,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B3" s="15" t="n">
         <f aca="false">x_cloud_y1</f>
@@ -5260,7 +5263,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B4" s="15" t="n">
         <f aca="false">$H$4</f>
@@ -5301,7 +5304,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B5" s="15" t="n">
         <f aca="false">$H$5</f>
@@ -5342,7 +5345,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B6" s="15" t="n">
         <f aca="false">x_crisk_p*x_crisk_s*B3</f>
@@ -5380,7 +5383,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B7" s="15" t="n">
         <f aca="false">B5+B6</f>
@@ -5452,7 +5455,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">B2+B3+B4+B7+B8</f>
@@ -5490,7 +5493,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -5516,7 +5519,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -5533,7 +5536,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -5553,22 +5556,22 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5648,7 +5651,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B18" s="14" t="n">
         <f aca="false">(x_tco_alt-(x_tco_cloud-(I3+I6)))/(I3+I6)</f>
